--- a/Packages/cn.etetet.twsmonster/Luban/Config/Datas/GameObjectPoolSettings.xlsx
+++ b/Packages/cn.etetet.twsmonster/Luban/Config/Datas/GameObjectPoolSettings.xlsx
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -235,7 +235,19 @@
     <t>如果 有最大显示&gt;0 这里必须配置</t>
   </si>
   <si>
-    <t>Monster</t>
+    <t>Monster_1</t>
+  </si>
+  <si>
+    <t>Monster_2</t>
+  </si>
+  <si>
+    <t>Monster_3</t>
+  </si>
+  <si>
+    <t>Monster_4</t>
+  </si>
+  <si>
+    <t>qiangzidan</t>
   </si>
 </sst>
 </file>
@@ -413,12 +425,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1250,8 +1262,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.25" style="2" customWidth="1"/>
     <col min="2" max="2" width="29.5" style="3" customWidth="1"/>
@@ -1363,6 +1375,86 @@
         <v>19</v>
       </c>
     </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>100</v>
+      </c>
+      <c r="E6" s="3">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>100</v>
+      </c>
+      <c r="E7" s="3">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Packages/cn.etetet.twsmonster/Luban/Config/Datas/GameObjectPoolSettings.xlsx
+++ b/Packages/cn.etetet.twsmonster/Luban/Config/Datas/GameObjectPoolSettings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>qiangzidan</t>
+  </si>
+  <si>
+    <t>banzhuan</t>
   </si>
 </sst>
 </file>
@@ -425,12 +428,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1262,7 +1265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.25" style="2" customWidth="1"/>
@@ -1455,6 +1458,26 @@
         <v>23</v>
       </c>
     </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Packages/cn.etetet.twsmonster/Luban/Config/Datas/GameObjectPoolSettings.xlsx
+++ b/Packages/cn.etetet.twsmonster/Luban/Config/Datas/GameObjectPoolSettings.xlsx
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -251,6 +251,33 @@
   </si>
   <si>
     <t>banzhuan</t>
+  </si>
+  <si>
+    <t>huixuanbiao</t>
+  </si>
+  <si>
+    <t>huojian</t>
+  </si>
+  <si>
+    <t>liulian</t>
+  </si>
+  <si>
+    <t>ranshaoping</t>
+  </si>
+  <si>
+    <t>zuantoudan</t>
+  </si>
+  <si>
+    <t>zuqiu</t>
+  </si>
+  <si>
+    <t>nengliangkuai_s</t>
+  </si>
+  <si>
+    <t>nengliangkuai_m</t>
+  </si>
+  <si>
+    <t>nengliangkuai_l</t>
   </si>
 </sst>
 </file>
@@ -428,12 +455,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1265,7 +1292,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.25" style="2" customWidth="1"/>
@@ -1478,6 +1505,186 @@
         <v>24</v>
       </c>
     </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>10</v>
+      </c>
+      <c r="F13" s="3">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="B14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3">
+        <v>10</v>
+      </c>
+      <c r="F15" s="3">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="B16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>5</v>
+      </c>
+      <c r="E16" s="3">
+        <v>10</v>
+      </c>
+      <c r="F16" s="3">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>50</v>
+      </c>
+      <c r="F17" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>50</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
+        <v>50</v>
+      </c>
+      <c r="F19" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
